--- a/erp_exchange/samples/updated_erp_export.xlsx
+++ b/erp_exchange/samples/updated_erp_export.xlsx
@@ -446,16 +446,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GRVL1000</t>
+          <t>BOOK1002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gravel</t>
+          <t>The Hobbit</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2300</v>
+        <v>12.99</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -464,16 +464,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DXTR1000</t>
+          <t>BOOK1001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1100</v>
+        <v>8.99</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
@@ -482,21 +482,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROAD2000</t>
+          <t>BOOK2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Road Bike</t>
+          <t>Dune</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Light carbon road bike</t>
+          <t>Science fiction novel by Frank Herbert</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3100</v>
+        <v>14.5</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>

--- a/erp_exchange/samples/updated_erp_export.xlsx
+++ b/erp_exchange/samples/updated_erp_export.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BOOK1002</t>
+          <t>9780547928227</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BOOK1001</t>
+          <t>9780451524935</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BOOK2001</t>
+          <t>9780441172719</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
